--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5175A1-42F6-4701-B06C-4AF044A70976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92165A0E-499C-4A6B-8FD1-941AF6D8CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 19-12-2025'!$A$1:$Y$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 29-01-2026'!$A$1:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1315,7 +1315,7 @@
         <v>55</v>
       </c>
       <c r="O30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="P30" t="s">
         <v>39</v>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92165A0E-499C-4A6B-8FD1-941AF6D8CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0FAB02-0853-4198-80B3-0EA7678D470E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 29-01-2026'!$A$1:$Y$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 02-02-2026'!$A$1:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0FAB02-0853-4198-80B3-0EA7678D470E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1A6B66-A9A0-470C-8FAC-4C660D519896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 02-02-2026'!$A$1:$Y$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 20-02-2026'!$A$1:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -572,9 +572,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -710,7 +710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -769,7 +769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -795,7 +795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -809,7 +809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -859,7 +859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -882,7 +882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -899,7 +899,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -913,7 +913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -927,7 +927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -955,7 +955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -969,7 +969,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -983,7 +983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>51</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1A6B66-A9A0-470C-8FAC-4C660D519896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AD796E-C260-4C1C-AB2A-AFE1F77BAFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 20-02-2026'!$A$1:$Y$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 04-03-2026'!$A$1:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AD796E-C260-4C1C-AB2A-AFE1F77BAFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E76AD6-C61F-465D-9C72-49CC075FF95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 04-03-2026'!$A$1:$Y$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 06-03-2026'!$A$1:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E76AD6-C61F-465D-9C72-49CC075FF95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2D61F5-A289-424D-A30F-007B23EBB0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2D61F5-A289-424D-A30F-007B23EBB0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDCE3BF-1347-41BC-9176-DB9F614019F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F567F7C-863D-4CAA-B40D-157C2FEC6513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3893D916-D459-45A0-8977-BE6138D2276C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3893D916-D459-45A0-8977-BE6138D2276C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67557CAE-7735-4DCE-989C-EDD094A96430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 09-03-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 11-03-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67557CAE-7735-4DCE-989C-EDD094A96430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B5FFF6-C750-4E30-BA24-3C805A5913F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B5FFF6-C750-4E30-BA24-3C805A5913F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD741265-0BA5-40FE-9FAB-D711B099E6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 11-03-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 20-03-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD741265-0BA5-40FE-9FAB-D711B099E6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9973D2D0-0120-48C1-B865-0C1CDD3D91BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 20-03-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 25-03-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9973D2D0-0120-48C1-B865-0C1CDD3D91BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9F31D-AA15-4020-B1DF-E0435578ACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 25-03-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 08-04-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9F31D-AA15-4020-B1DF-E0435578ACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A874B84-16D3-47A6-BDFA-A0D0BF6246D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 08-04-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 10-04-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A874B84-16D3-47A6-BDFA-A0D0BF6246D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404988A3-4747-4AB6-BCF5-1D0A8B5C266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404988A3-4747-4AB6-BCF5-1D0A8B5C266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB15B56C-DD6B-4DA8-B029-ED5146C804B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 10-04-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 14-04-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB15B56C-DD6B-4DA8-B029-ED5146C804B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85FA98-C3A4-47A3-BE9F-8AA4E4705299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 14-04-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 24-04-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85FA98-C3A4-47A3-BE9F-8AA4E4705299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860731F0-570D-4E65-9AF9-76B8A84D57E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>KBMarkør (MedTek Huset)</t>
   </si>
   <si>
-    <t>LABKAII (Dedalus)</t>
+    <t>LABKAII (Dedalus Healthcare Denmark)</t>
   </si>
   <si>
     <t>Labsys (Rigshospitalet)</t>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860731F0-570D-4E65-9AF9-76B8A84D57E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DAAD4C-DCDA-4881-A590-38EA93C3B3D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 24-04-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 27-04-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DAAD4C-DCDA-4881-A590-38EA93C3B3D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E97C7A-A05A-4C2A-851E-D947A287876B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 27-04-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 06-05-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E97C7A-A05A-4C2A-851E-D947A287876B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB5A697-8482-42CA-B35A-0A41DACB3F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 06-05-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 01-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB5A697-8482-42CA-B35A-0A41DACB3F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFAC5A6-E6F8-4EFE-B41A-8E6A572A405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 01-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 02-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFAC5A6-E6F8-4EFE-B41A-8E6A572A405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A70078-FCAE-4554-B17A-F41D51829882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A70078-FCAE-4554-B17A-F41D51829882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99578362-1A60-4DE9-A683-A738CDB7CB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 02-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 05-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92165A0E-499C-4A6B-8FD1-941AF6D8CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3A9C6B-E2A8-49EF-9841-BB60570A3836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877F5626-DADF-46CA-ADA7-C08CE65BB8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0254F-1EFF-4C19-9A57-C46A0025B6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0254F-1EFF-4C19-9A57-C46A0025B6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E6351A-993B-422A-B9B4-2941C40F2F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E6351A-993B-422A-B9B4-2941C40F2F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5481C52-ADBB-4FF7-B7F9-A2D97B95B415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 09-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 15-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5481C52-ADBB-4FF7-B7F9-A2D97B95B415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F13F00-6CB0-4859-8594-A0C35FE0534E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 15-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 22-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F13F00-6CB0-4859-8594-A0C35FE0534E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D25B9E-C9F0-435D-A493-26288B0F300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 22-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 23-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D25B9E-C9F0-435D-A493-26288B0F300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85238511-2420-4565-B6FA-DF967CA48C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F13F00-6CB0-4859-8594-A0C35FE0534E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D977FA0-4883-47A9-B58B-EB1F6BCD66A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 22-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 23-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D977FA0-4883-47A9-B58B-EB1F6BCD66A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1DEEE-7BE3-4CDC-AE9D-1FCC0B9CDFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 23-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 25-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1DEEE-7BE3-4CDC-AE9D-1FCC0B9CDFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDB18EE-2722-4758-BCF4-44A6A8FAAD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 25-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 30-06-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDB18EE-2722-4758-BCF4-44A6A8FAAD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F7B34B-0F94-4F75-998B-7D02E36795FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F7B34B-0F94-4F75-998B-7D02E36795FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DF1C1-DF52-4882-98BD-E94DFE6ECD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 30-06-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 01-07-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DF1C1-DF52-4882-98BD-E94DFE6ECD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC13D63-7A35-4B9D-86F0-FC4DDD354222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 01-07-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 02-07-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DF1C1-DF52-4882-98BD-E94DFE6ECD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5689213-F689-4AF7-B9F2-45339A7C1394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 01-07-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 03-07-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC13D63-7A35-4B9D-86F0-FC4DDD354222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5449BCC-8202-4CF4-BDA4-85978D1AFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 02-07-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 03-07-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5449BCC-8202-4CF4-BDA4-85978D1AFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942B3456-0628-420D-B8A0-6DB7F13CC855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 03-07-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 09-07-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942B3456-0628-420D-B8A0-6DB7F13CC855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD188E-688C-42FC-A085-8499DA11E333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 09-07-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 19-08-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD188E-688C-42FC-A085-8499DA11E333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E2FD9-FFFA-4E09-A2B8-0C8041651627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 19-08-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 21-08-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E2FD9-FFFA-4E09-A2B8-0C8041651627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F33EE0-3229-40EB-A482-9B22A1879AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 21-08-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 27-08-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -575,9 +575,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -809,7 +809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -859,7 +859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -882,7 +882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -930,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -944,7 +944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -958,7 +958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -972,7 +972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -989,7 +989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F33EE0-3229-40EB-A482-9B22A1879AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD992D08-5823-4C9E-8CD6-1FE080C2C3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 27-08-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 02-09-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD992D08-5823-4C9E-8CD6-1FE080C2C3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334E2EF1-998E-43FD-B4EC-1A7F24C45DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 02-09-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 06-09-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334E2EF1-998E-43FD-B4EC-1A7F24C45DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03CF9D2-C595-4D90-9EE8-5189F6D7A321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03CF9D2-C595-4D90-9EE8-5189F6D7A321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CC15F3-A981-47FE-88D4-57DD0DDF4A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 06-09-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 07-09-2026'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CC15F3-A981-47FE-88D4-57DD0DDF4A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BBD6DF-991A-4CC8-9E33-F19589313762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Laboratoriesystemer">'Opdateret d. 07-09-2026'!$A$1:$X$31</definedName>
+    <definedName name="Laboratoriesystemer">'Opdateret d. 09-09-2026'!$A$1:$Y$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="72">
   <si>
     <t>Standard</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Labsys (Rigshospitalet)</t>
   </si>
   <si>
+    <t>LabVantage Medical Suite (Whitelake Software Point OY)</t>
+  </si>
+  <si>
     <t>LabWare LIMS (LabWare Nordic)</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>Godkendt</t>
   </si>
   <si>
+    <t>Tester</t>
+  </si>
+  <si>
     <t>Ikke Godkendt</t>
   </si>
   <si>
@@ -139,9 +145,6 @@
     <t>REQ01 (Q0132K)</t>
   </si>
   <si>
-    <t>Tester</t>
-  </si>
-  <si>
     <t>Patologirekvisition</t>
   </si>
   <si>
@@ -233,6 +236,9 @@
   </si>
   <si>
     <t>XRPT05 (XR0532M)</t>
+  </si>
+  <si>
+    <t>WS-klient</t>
   </si>
 </sst>
 </file>
@@ -574,10 +580,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -650,695 +656,736 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" t="s">
+        <v>28</v>
+      </c>
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="R8" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
+      <c r="S9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="P2" t="s">
+      <c r="W11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="T13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" t="s">
-        <v>27</v>
-      </c>
-      <c r="S3" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="U14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" t="s">
+        <v>28</v>
+      </c>
+      <c r="S15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U15" t="s">
+        <v>28</v>
+      </c>
+      <c r="V15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" t="s">
-        <v>27</v>
-      </c>
-      <c r="T6" t="s">
-        <v>28</v>
-      </c>
-      <c r="U6" t="s">
-        <v>27</v>
-      </c>
-      <c r="X6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" t="s">
+        <v>28</v>
+      </c>
+      <c r="W18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>27</v>
-      </c>
-      <c r="R8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B19" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="R9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="W19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>43</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B20" t="s">
         <v>44</v>
       </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="V11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>28</v>
+      </c>
+      <c r="U20" t="s">
+        <v>30</v>
+      </c>
+      <c r="V20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="R22" t="s">
+        <v>28</v>
+      </c>
+      <c r="S22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="R23" t="s">
+        <v>28</v>
+      </c>
+      <c r="S23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" t="s">
+        <v>28</v>
+      </c>
+      <c r="U27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="S12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="T28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="P30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B31" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="T14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-      <c r="T15" t="s">
-        <v>27</v>
-      </c>
-      <c r="U15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="V18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="V19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" t="s">
-        <v>27</v>
-      </c>
-      <c r="T20" t="s">
-        <v>28</v>
-      </c>
-      <c r="U20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" t="s">
-        <v>27</v>
-      </c>
-      <c r="X21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>27</v>
-      </c>
-      <c r="R22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-      <c r="O25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-      <c r="I26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" t="s">
-        <v>27</v>
-      </c>
-      <c r="T27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
-      </c>
-      <c r="S28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" t="s">
-        <v>27</v>
-      </c>
-      <c r="O29" t="s">
-        <v>27</v>
-      </c>
-      <c r="X29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-      <c r="O30" t="s">
-        <v>27</v>
-      </c>
-      <c r="X30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="T31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>49</v>
       </c>
-      <c r="C31" t="s">
-        <v>52</v>
-      </c>
-      <c r="M31" t="s">
-        <v>38</v>
-      </c>
-      <c r="S31" t="s">
-        <v>27</v>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/html/Laboratoriesystemer_excel.XLSX
+++ b/html/Laboratoriesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BBD6DF-991A-4CC8-9E33-F19589313762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A740B1-52DF-44FD-A917-9A5FE515E9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
